--- a/Entregue milestone 2/G14_8220849_8220238_8200066_8230153/ProductBacklog.xlsx
+++ b/Entregue milestone 2/G14_8220849_8220238_8200066_8230153/ProductBacklog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guiba\Desktop\LDS\ficheiros para milestone 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guiba\Desktop\LDS\Entregue milestone 2\G14_8220849_8220238_8200066_8230153\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012C3CF4-DFFE-4104-8418-8A08C898FFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D3E648-813D-45B3-932A-0718FB676542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{982013A5-BAA1-47D2-B87C-A47FCA2ABBE8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="116">
   <si>
     <t>Descrição</t>
   </si>
@@ -418,6 +418,15 @@
   </si>
   <si>
     <t>Guilherme</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Essencial</t>
+  </si>
+  <si>
+    <t>Média</t>
   </si>
 </sst>
 </file>
@@ -561,7 +570,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -591,6 +600,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -602,6 +614,40 @@
         <left style="thin">
           <color theme="0"/>
         </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
         <right style="thin">
           <color theme="0"/>
         </right>
@@ -618,51 +664,6 @@
           <color theme="0"/>
         </left>
         <right/>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0"/>
-        </left>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0"/>
-        </left>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="0"/>
-        </left>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
         <top style="thin">
           <color theme="0"/>
         </top>
@@ -783,11 +784,11 @@
     <tableColumn id="1" xr3:uid="{920B1D59-6FD0-416D-9FF2-FEE9D0983694}" name="Título" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{680D0AC6-4CE8-48EF-BCFB-03948140A6E2}" name="Descrição" dataDxfId="6"/>
     <tableColumn id="3" xr3:uid="{1647D1E5-9627-4862-9C3D-8691065746F2}" name="Critérios de Aceitação" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{4490F14B-200A-4E29-8874-01BE4153AF22}" name="Notas/Tarefas Técnicas" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{B4C3319D-1302-4ECA-AEFD-266A6692D8C3}" name="Prioridade" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{666559DA-E2DD-419E-8EBC-4F1F0933AB1E}" name="Story Points" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{E81AB74D-11A4-4854-A3CF-BD62490C1E4E}" name="Responsável" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{FC635F6F-64ED-4D11-942C-0774FC7A12AD}" name="Estado" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{4490F14B-200A-4E29-8874-01BE4153AF22}" name="Notas/Tarefas Técnicas" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{B4C3319D-1302-4ECA-AEFD-266A6692D8C3}" name="Prioridade" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{666559DA-E2DD-419E-8EBC-4F1F0933AB1E}" name="Story Points" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{E81AB74D-11A4-4854-A3CF-BD62490C1E4E}" name="Responsável" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{FC635F6F-64ED-4D11-942C-0774FC7A12AD}" name="Estado" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1110,10 +1111,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AE6CC1C-EFAF-48DF-83E5-D6572C671D8C}">
-  <dimension ref="B3:I28"/>
+  <dimension ref="B2:I28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.85546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="71.140625" style="1" customWidth="1"/>
@@ -1125,6 +1126,7 @@
     <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="2:9" ht="33" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>7</v>
@@ -1164,8 +1166,12 @@
       <c r="E4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="F4" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G4" s="13">
+        <v>3</v>
+      </c>
       <c r="H4" s="11" t="s">
         <v>109</v>
       </c>
@@ -1186,8 +1192,12 @@
       <c r="E5" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="F5" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="13">
+        <v>3</v>
+      </c>
       <c r="H5" s="12" t="s">
         <v>110</v>
       </c>
@@ -1208,8 +1218,12 @@
       <c r="E6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
+      <c r="F6" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G6" s="13">
+        <v>3</v>
+      </c>
       <c r="H6" s="12" t="s">
         <v>111</v>
       </c>
@@ -1230,8 +1244,12 @@
       <c r="E7" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="F7" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G7" s="13">
+        <v>8</v>
+      </c>
       <c r="H7" s="12" t="s">
         <v>112</v>
       </c>
@@ -1252,8 +1270,12 @@
       <c r="E8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
+      <c r="F8" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G8" s="13">
+        <v>1</v>
+      </c>
       <c r="H8" s="12" t="s">
         <v>111</v>
       </c>
@@ -1274,8 +1296,12 @@
       <c r="E9" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
+      <c r="F9" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G9" s="13">
+        <v>3</v>
+      </c>
       <c r="H9" s="12" t="s">
         <v>109</v>
       </c>
@@ -1296,8 +1322,12 @@
       <c r="E10" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="F10" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G10" s="13">
+        <v>5</v>
+      </c>
       <c r="H10" s="12" t="s">
         <v>110</v>
       </c>
@@ -1318,8 +1348,12 @@
       <c r="E11" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
+      <c r="F11" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G11" s="13">
+        <v>3</v>
+      </c>
       <c r="H11" s="12" t="s">
         <v>112</v>
       </c>
@@ -1340,8 +1374,12 @@
       <c r="E12" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+      <c r="F12" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G12" s="13">
+        <v>3</v>
+      </c>
       <c r="H12" s="12" t="s">
         <v>110</v>
       </c>
@@ -1362,8 +1400,12 @@
       <c r="E13" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
+      <c r="F13" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G13" s="13">
+        <v>5</v>
+      </c>
       <c r="H13" s="12" t="s">
         <v>111</v>
       </c>
@@ -1384,8 +1426,12 @@
       <c r="E14" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
+      <c r="F14" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G14" s="13">
+        <v>5</v>
+      </c>
       <c r="H14" s="12" t="s">
         <v>112</v>
       </c>
@@ -1406,8 +1452,12 @@
       <c r="E15" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
+      <c r="F15" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="13">
+        <v>5</v>
+      </c>
       <c r="H15" s="11" t="s">
         <v>109</v>
       </c>
@@ -1428,8 +1478,12 @@
       <c r="E16" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
+      <c r="F16" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G16" s="13">
+        <v>8</v>
+      </c>
       <c r="H16" s="12" t="s">
         <v>111</v>
       </c>
@@ -1450,8 +1504,12 @@
       <c r="E17" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
+      <c r="F17" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G17" s="13">
+        <v>5</v>
+      </c>
       <c r="H17" s="12" t="s">
         <v>110</v>
       </c>
@@ -1472,8 +1530,12 @@
       <c r="E18" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+      <c r="F18" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G18" s="13">
+        <v>5</v>
+      </c>
       <c r="H18" s="12" t="s">
         <v>112</v>
       </c>
@@ -1494,8 +1556,12 @@
       <c r="E19" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="F19" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G19" s="13">
+        <v>2</v>
+      </c>
       <c r="H19" s="12" t="s">
         <v>109</v>
       </c>
@@ -1516,8 +1582,12 @@
       <c r="E20" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
+      <c r="F20" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" s="13">
+        <v>2</v>
+      </c>
       <c r="H20" s="12" t="s">
         <v>110</v>
       </c>
@@ -1538,8 +1608,12 @@
       <c r="E21" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
+      <c r="F21" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="G21" s="13">
+        <v>5</v>
+      </c>
       <c r="H21" s="11" t="s">
         <v>111</v>
       </c>
@@ -1560,8 +1634,12 @@
       <c r="E22" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+      <c r="F22" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G22" s="13">
+        <v>8</v>
+      </c>
       <c r="H22" s="12" t="s">
         <v>109</v>
       </c>
@@ -1582,8 +1660,12 @@
       <c r="E23" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
+      <c r="F23" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G23" s="13">
+        <v>8</v>
+      </c>
       <c r="H23" s="12" t="s">
         <v>112</v>
       </c>
@@ -1591,7 +1673,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" ht="90" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
         <v>49</v>
       </c>
@@ -1604,8 +1686,12 @@
       <c r="E24" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
+      <c r="F24" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="G24" s="13">
+        <v>2</v>
+      </c>
       <c r="H24" s="11" t="s">
         <v>112</v>
       </c>
@@ -1626,8 +1712,12 @@
       <c r="E25" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
+      <c r="F25" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G25" s="13">
+        <v>2</v>
+      </c>
       <c r="H25" s="11" t="s">
         <v>110</v>
       </c>
@@ -1648,8 +1738,12 @@
       <c r="E26" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
+      <c r="F26" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G26" s="13">
+        <v>5</v>
+      </c>
       <c r="H26" s="11" t="s">
         <v>109</v>
       </c>
@@ -1670,8 +1764,12 @@
       <c r="E27" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
+      <c r="F27" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G27" s="13">
+        <v>5</v>
+      </c>
       <c r="H27" s="11" t="s">
         <v>111</v>
       </c>
@@ -1692,8 +1790,12 @@
       <c r="E28" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
+      <c r="F28" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G28" s="13">
+        <v>5</v>
+      </c>
       <c r="H28" s="11" t="s">
         <v>110</v>
       </c>
